--- a/outputs/recomendaciones_tfidf.xlsx
+++ b/outputs/recomendaciones_tfidf.xlsx
@@ -484,35 +484,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0348</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y</t>
+          <t>Propiedad intelectual</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.14318</v>
+        <v>0.147837</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_valencia/txt/22548_propiedad_intelectual.txt</t>
         </is>
       </c>
     </row>
@@ -532,35 +532,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>doc_0088</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22548_propiedad_intelectual</t>
+          <t>EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.118101</v>
+        <v>0.143228</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/22548_propiedad_intelectual.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
     </row>
@@ -580,35 +580,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0270</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Propiedad industrial e intelectual (28)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.097577</v>
+        <v>0.10233</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_valencia/txt/1103_propiedad_industrial_e_intelectual_28.txt</t>
         </is>
       </c>
     </row>
@@ -628,35 +628,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>doc_0010</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1103_propiedad_industrial_e_intelectual_28</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.091019</v>
+        <v>0.097568</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/1103_propiedad_industrial_e_intelectual_28.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>doc_0334</t>
+          <t>doc_0201</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -700,11 +700,11 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.084353</v>
+        <v>0.084345</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe COTEC 2014.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe COTEC 2014.pdf</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.07895199999999999</v>
+        <v>0.078976</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.078559</v>
+        <v>0.078434</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>doc_0348</t>
+          <t>doc_0215</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -844,11 +844,11 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.072602</v>
+        <v>0.07262</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22691_manual_diagrama_integral_de_startups</t>
+          <t>Manual Diagrama integral de startups</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.072294</v>
+        <v>0.072255</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>doc_0149</t>
+          <t>doc_0016</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -940,11 +940,11 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.07074900000000001</v>
+        <v>0.070767</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Mejoras en las deducciones fiscales por IDiGuía.pdf</t>
+          <t>data/raw/ceei_elche/original/Mejoras en las deducciones fiscales por IDiGuía.pdf</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.228107</v>
+        <v>0.230606</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>doc_0401</t>
+          <t>doc_0280</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>22691_manual_diagrama_integral_de_startups</t>
+          <t>Lean Startup para el Escalado de Startups</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1027,20 +1027,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.116688</v>
+        <v>0.12437</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/22691_manual_diagrama_integral_de_startups.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14625_lean_startup_para_el_escalado_de_startups.txt</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>doc_0020</t>
+          <t>doc_0401</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14625_lean_startup_para_el_escalado_de_startups</t>
+          <t>Manual Diagrama integral de startups</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1075,20 +1075,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.105161</v>
+        <v>0.117059</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14625_lean_startup_para_el_escalado_de_startups.txt</t>
+          <t>documentos_ceei_valencia/22691_manual_diagrama_integral_de_startups.pdf</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>22544_alianzas_estrategicas_entre_empresas_y_startups_como_construir_relaciones_que_beneficien_a</t>
+          <t>Alianzas estratégicas entre empresas y startups Cómo construir relaciones que beneficien a ambas partes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.101206</v>
+        <v>0.099033</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1180,11 +1180,11 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.09854400000000001</v>
+        <v>0.09854300000000001</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>doc_0332</t>
+          <t>doc_0199</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1228,11 +1228,11 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.07985200000000001</v>
+        <v>0.07985299999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1276,11 +1276,11 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.074355</v>
+        <v>0.07435799999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>doc_0186</t>
+          <t>doc_0053</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1324,11 +1324,11 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.072785</v>
+        <v>0.07277699999999999</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Internacionalización.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Consultoría de Internacionalización.pdf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>23069_plan_de_innovacion</t>
+          <t>Plan de innovación</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1372,7 +1372,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.067258</v>
+        <v>0.066953</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>doc_0304</t>
+          <t>doc_0171</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/KPIs_ Indicadores Clave de RendimientoINFOGRAFÍAS.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/KPIs_ Indicadores Clave de RendimientoINFOGRAFÍAS.pdf</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>doc_0340</t>
+          <t>doc_0207</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro de AESEC_Esta acción ha sido desarrollada en colabo.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro de AESEC_Esta acción ha sido desarrollada en colabo.pdf</t>
         </is>
       </c>
     </row>
@@ -1492,22 +1492,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>doc_0365</t>
+          <t>doc_0337</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Despacho Profesional_ Servicios de Consultoría</t>
+          <t>Despacho Profesional: Servicios de Consultoría Modelo de Negocio</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Modelos_de_Negocio_texto</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1516,11 +1516,11 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.09307699999999999</v>
+        <v>0.097848</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Despacho Profesional_ Servicios de Consultoría.txt</t>
+          <t>data/raw/ceei_valencia/txt/21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio.txt</t>
         </is>
       </c>
     </row>
@@ -1540,22 +1540,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>doc_0077</t>
+          <t>doc_0232</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio</t>
+          <t>Despacho Profesional: Servicios de Consultoría</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Modelos_de_Negocio_texto</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1564,11 +1564,11 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.08467</v>
+        <v>0.092806</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/21519_despacho_profesional_servicios_de_consultoría_modelo_de_negocio.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Despacho Profesional_ Servicios de Consultoría.txt</t>
         </is>
       </c>
     </row>
@@ -1588,35 +1588,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>doc_0339</t>
+          <t>doc_0285</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol</t>
+          <t>Servicios profesionales empresariales Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.07721699999999999</v>
+        <v>0.087503</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
         </is>
       </c>
     </row>
@@ -1636,35 +1636,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>doc_0025</t>
+          <t>doc_0206</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.07607999999999999</v>
+        <v>0.077219</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ Retos para la creación de valor a futuro Comarca de la Vega BajaEsta acción ha sido desarrol.pdf</t>
         </is>
       </c>
     </row>
@@ -1684,35 +1684,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0311</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Guía de Digitalización para Pymes Manual de Gestión Empresarial elaborado por Leonard Pera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.07066600000000001</v>
+        <v>0.07332900000000001</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_valencia/txt/18339_guía_de_digitalización_para_pymes_manual_de_gestión_empresarial_elaborado_por_leonard_pera.txt</t>
         </is>
       </c>
     </row>
@@ -1732,12 +1732,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>doc_0188</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Consultoría de Proyectos y Captación de Financiación</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1756,11 +1756,11 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.07052799999999999</v>
+        <v>0.070669</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Proyectos y Captación de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -1780,22 +1780,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>doc_0394</t>
+          <t>doc_0055</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio</t>
+          <t>Consultoría de Proyectos y Captación de Financiación</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1804,11 +1804,11 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.068131</v>
+        <v>0.07052799999999999</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Consultoría de Proyectos y Captación de Financiación.pdf</t>
         </is>
       </c>
     </row>
@@ -1828,35 +1828,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>doc_0337</t>
+          <t>doc_0355</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_</t>
+          <t>Consultoría en gestión del agua y reciclaje Modelo de Negocio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Informes_y_Publicaciones</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.067078</v>
+        <v>0.068685</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
+          <t>data/raw/ceei_valencia/txt/23078_consultoría_en_gestión_del_agua_y_reciclaje_modelo_de_negocio.txt</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1876,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>doc_0186</t>
+          <t>doc_0394</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Consultoría de Internacionalización</t>
+          <t>Networking, mentoring y techscouting Tres modelos de innovación abierta para tu negocio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1900,11 +1900,11 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.066608</v>
+        <v>0.06843200000000001</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Consultoría de Internacionalización.pdf</t>
+          <t>documentos_ceei_valencia/20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio.pdf</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>doc_0348</t>
+          <t>doc_0215</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.09193999999999999</v>
+        <v>0.09194099999999999</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resumen HUB de Innovación Colaborativa.pdf</t>
         </is>
       </c>
     </row>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20407_networking_mentoring_y_techscouting_tres_modelos_de_innovacion_abierta_para_tu_negocio</t>
+          <t>Networking, mentoring y techscouting Tres modelos de innovación abierta para tu negocio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.074974</v>
+        <v>0.07438699999999999</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>doc_0414</t>
+          <t>doc_0285</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>23032_servicios_de_fotografia_y_video_para_empresas</t>
+          <t>Servicios profesionales empresariales Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2035,20 +2035,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.069517</v>
+        <v>0.071546</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>documentos_ceei_valencia/23032_servicios_de_fotografia_y_video_para_empresas.pdf</t>
+          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>doc_0254</t>
+          <t>doc_0414</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2092,11 +2092,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.069206</v>
+        <v>0.06922200000000001</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Servicios de Fotografía y Vídeo para Empresas.pdf</t>
+          <t>documentos_ceei_valencia/23032_servicios_de_fotografia_y_video_para_empresas.pdf</t>
         </is>
       </c>
     </row>
@@ -2116,35 +2116,35 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>doc_0025</t>
+          <t>doc_0121</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Servicios de Fotografía y Vídeo para Empresas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.06331000000000001</v>
+        <v>0.069207</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/14644_servicios_profesionales_empresariales_modelo_de_negocio_de_actividades_empresariales.txt</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Servicios de Fotografía y Vídeo para Empresas.pdf</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2188,11 +2188,11 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.062062</v>
+        <v>0.062067</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2236,11 +2236,11 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.060664</v>
+        <v>0.060666</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>doc_0192</t>
+          <t>doc_0059</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2284,11 +2284,11 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.059662</v>
+        <v>0.059664</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Despachos Profesionales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Despachos Profesionales.pdf</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>23019_centro_especializado_en_vehiculos_electricos</t>
+          <t>Centro especializado en vehículos eléctricos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.058917</v>
+        <v>0.05887</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>doc_0349</t>
+          <t>doc_0216</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2380,11 +2380,11 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.058872</v>
+        <v>0.058869</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio/Centro especializado en vehículos eléctricos.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio/Centro especializado en vehículos eléctricos.pdf</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>doc_0323</t>
+          <t>doc_0190</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2428,11 +2428,11 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0.282578</v>
+        <v>0.282572</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>doc_0337</t>
+          <t>doc_0204</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2476,11 +2476,11 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.138386</v>
+        <v>0.138382</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe de resultados 2023_ HUB Nueva Ruralidad RegenerativaLo rural como punta de lanza de la transformación económica_.pdf</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>doc_0346</t>
+          <t>doc_0213</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2524,11 +2524,11 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.121609</v>
+        <v>0.121612</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resultados fase entender HUB Innovación Colaborativa Territorial 2023- Nueva Ruralidad Regenerativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resultados fase entender HUB Innovación Colaborativa Territorial 2023- Nueva Ruralidad Regenerativa.pdf</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>doc_0369</t>
+          <t>doc_0236</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2572,11 +2572,11 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.113158</v>
+        <v>0.113152</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Economía Circular.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Economía Circular.txt</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>doc_0272</t>
+          <t>doc_0139</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2620,11 +2620,11 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0.109779</v>
+        <v>0.10977</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Turismo Rural.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Turismo Rural.pdf</t>
         </is>
       </c>
     </row>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>doc_0032</t>
+          <t>doc_0292</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>14822_economía_circular_modelo_de_negocio</t>
+          <t>Economía Circular Modelo de Negocio</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2668,7 +2668,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0.095191</v>
+        <v>0.109733</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>doc_0347</t>
+          <t>doc_0214</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2716,11 +2716,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>0.088564</v>
+        <v>0.088565</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Resultados proyecto piloto HUB Innovación Colaborativa Territorial 2021 - 2022.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Resultados proyecto piloto HUB Innovación Colaborativa Territorial 2021 - 2022.pdf</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>doc_0326</t>
+          <t>doc_0193</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2764,11 +2764,11 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>0.084052</v>
+        <v>0.08405899999999999</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/EBC_s generadas en el entorno de los Parque Científicos de la Provincia de Alicante y su relación con RIS3-CVInformes y .pdf</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>doc_0330</t>
+          <t>doc_0197</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe 2023_ Ecosistema local energético colaborativo_ autosuficiente_ eficiente y sostenible en Salinas_Resultados de .pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe 2023_ Ecosistema local energético colaborativo_ autosuficiente_ eficiente y sostenible en Salinas_Resultados de .pdf</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>doc_0211</t>
+          <t>doc_0078</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Empresas de Servicios Sociales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Empresas de Servicios Sociales.pdf</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>doc_0135</t>
+          <t>doc_0002</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2908,11 +2908,11 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.189507</v>
+        <v>0.189503</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guia de responsabilidad social de la empresaGuía d.pdf</t>
+          <t>data/raw/ceei_elche/original/Guia de responsabilidad social de la empresaGuía d.pdf</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>22980_sostenibilidad_decidir_hoy_para_no_limitar_el_crecimiento_manana</t>
+          <t>Sostenibilidad: decidir hoy para no limitar el crecimiento mañana</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.127742</v>
+        <v>0.127551</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>doc_0147</t>
+          <t>doc_0014</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3004,11 +3004,11 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.104516</v>
+        <v>0.104518</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Trámites de constitución de empresa.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Trámites de constitución de empresa.pdf</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>doc_0372</t>
+          <t>doc_0239</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3052,11 +3052,11 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.08568199999999999</v>
+        <v>0.08612300000000001</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Empresa de Tiempo Libre.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Empresa de Tiempo Libre.txt</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3076,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>doc_0084</t>
+          <t>doc_0344</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>22448_empresa_de_tiempo_libre_modelo_de_negocio_de_actividades_empresariales</t>
+          <t>Empresa de Tiempo Libre Modelo de Negocio de Actividades Empresariales</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.080846</v>
+        <v>0.076793</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>doc_0211</t>
+          <t>doc_0078</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Empresas de Servicios Sociales.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Empresas de Servicios Sociales.pdf</t>
         </is>
       </c>
     </row>
@@ -3172,22 +3172,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>doc_0040</t>
+          <t>doc_0245</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18162_la_sostenibilidad_en_la_empresa._aplicación_práctica_a_las_pymes_61_manual_elaborado_por_joan_ramon_sanchis_palacio_vane</t>
+          <t>Gestión Cultural</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Modelos_de_Negocio_texto</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3196,11 +3196,11 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.07285700000000001</v>
+        <v>0.072198</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/18162_la_sostenibilidad_en_la_empresa._aplicación_práctica_a_las_pymes_61_manual_elaborado_por_joan_ramon_sanchis_palacio_vane.txt</t>
+          <t>data/raw/ceei_elche/pdf/Modelos_de_Negocio_texto/Gestión Cultural.txt</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>doc_0378</t>
+          <t>doc_0340</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Modelos_de_Negocio_texto</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3244,11 +3244,11 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.072198</v>
+        <v>0.067505</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Modelos_de_Negocio_texto/Gestión Cultural.txt</t>
+          <t>data/raw/ceei_valencia/txt/22444_gestión_cultural.txt</t>
         </is>
       </c>
     </row>
@@ -3268,35 +3268,35 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>doc_0080</t>
+          <t>doc_0175</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>22444_gestión_cultural</t>
+          <t>Pasos para realizar el Plan Social Media de tu negocio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Infografias</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.06911</v>
+        <v>0.06705899999999999</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/22444_gestión_cultural.txt</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Pasos para realizar el Plan Social Media de tu negocio.pdf</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>doc_0308</t>
+          <t>doc_0200</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pasos para realizar el Plan Social Media de tu negocio</t>
+          <t>Informe Benchmarking CEEI Elche 2020_ Impacto COVID19_ Claves para la Recuperación Económica 2021Informes y estudios</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Infografias</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3340,11 +3340,11 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.067055</v>
+        <v>0.06475400000000001</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Pasos para realizar el Plan Social Media de tu negocio.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2020_ Impacto COVID19_ Claves para la Recuperación Económica 2021Informes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>doc_0123</t>
+          <t>doc_0383</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>6891_metodología_lean_startup_41_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Metodología Lean Startup (41) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3388,7 +3388,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.145535</v>
+        <v>0.163419</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23022_innovacion_interna_metodologias_agiles_de_innovacion_ii</t>
+          <t>Innovación interna: metodologías ágiles de innovación II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.144804</v>
+        <v>0.144247</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>doc_0020</t>
+          <t>doc_0280</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>14625_lean_startup_para_el_escalado_de_startups</t>
+          <t>Lean Startup para el Escalado de Startups</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.124826</v>
+        <v>0.139989</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>doc_0325</t>
+          <t>doc_0192</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -3532,11 +3532,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.117068</v>
+        <v>0.117011</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Business Innovation Kit-Bikceei 2020.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Business Innovation Kit-Bikceei 2020.pdf</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>doc_0278</t>
+          <t>doc_0145</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3580,11 +3580,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0.106036</v>
+        <v>0.106068</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/3 Nuevas metodologías BIK para empresas y emprendedoresPara emprendedores_ startups y pymes.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/3 Nuevas metodologías BIK para empresas y emprendedoresPara emprendedores_ startups y pymes.pdf</t>
         </is>
       </c>
     </row>
@@ -3604,35 +3604,35 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>doc_0013</t>
+          <t>doc_0167</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>11900_producto_mínimo_viable_51_autor_roberto_touza</t>
+          <t>Gestión Ágil y StartupPara emprendedores y startups</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Infografias</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.093488</v>
+        <v>0.09074400000000001</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/11900_producto_mínimo_viable_51_autor_roberto_touza.txt</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Gestión Ágil y StartupPara emprendedores  y startups.pdf</t>
         </is>
       </c>
     </row>
@@ -3652,12 +3652,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>doc_0300</t>
+          <t>doc_0191</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Gestión Ágil y StartupPara emprendedores y startups</t>
+          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Infografias</t>
+          <t>Informes_y_Publicaciones</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3676,11 +3676,11 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0.090716</v>
+        <v>0.088841</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Gestión Ágil y StartupPara emprendedores  y startups.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>doc_0324</t>
+          <t>doc_0199</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios</t>
+          <t>Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3724,11 +3724,11 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.088819</v>
+        <v>0.085817</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis sobre metodologías y herramientas de innovación del ecosistema emprendedor de CVInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>doc_0332</t>
+          <t>doc_0211</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios</t>
+          <t>Informe GEM 2018-19 sobre el ecosistema emprendedor en España</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3772,11 +3772,11 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.085816</v>
+        <v>0.083492</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Informe Benchmarking CEEI Elche 2018-2019_ Análisis sobre metodologías y herramientas de innovación_Informes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Informe GEM 2018-19 sobre el ecosistema emprendedor en España.pdf</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20565_manual_scaleup_y_softlanding_scaleup_y_softlanding_internacional</t>
+          <t>Manual ScaleUp y softlanding ScaleUp y softlanding internacional</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Documento_PDF</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.083527</v>
+        <v>0.083402</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>doc_0311</t>
+          <t>doc_0178</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3868,11 +3868,11 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.07148400000000001</v>
+        <v>0.071424</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Recursos Gratuitos_ Creación y Crecimiento de empresasCerca de 600 recursos para emprendedores_ startups y pymes.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Recursos Gratuitos_ Creación y Crecimiento de empresasCerca de 600 recursos para emprendedores_ startups y pymes.pdf</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>doc_0140</t>
+          <t>doc_0007</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3916,11 +3916,11 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0.068969</v>
+        <v>0.068967</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche/Guía de Apoyo Fuentes de Financiación.pdf</t>
+          <t>data/raw/ceei_elche/original/Guía de Apoyo Fuentes de Financiación.pdf</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>doc_0227</t>
+          <t>doc_0094</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3964,11 +3964,11 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.056072</v>
+        <v>0.056077</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Gestoría Administrativa.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Gestoría Administrativa.pdf</t>
         </is>
       </c>
     </row>
@@ -3988,12 +3988,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>doc_0101</t>
+          <t>doc_0361</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>244_plan_y_presupuesto_de_comunicación_6_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Plan y Presupuesto de Comunicación (6) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.052118</v>
+        <v>0.052879</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>doc_0328</t>
+          <t>doc_0195</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4060,11 +4060,11 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.050671</v>
+        <v>0.050662</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Estudio sobre creación de un Fondo de Garantía para la concesión de microcréditosInformes y estudios.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Estudio sobre creación de un Fondo de Garantía para la concesión de microcréditosInformes y estudios.pdf</t>
         </is>
       </c>
     </row>
@@ -4084,35 +4084,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>doc_0183</t>
+          <t>doc_0370</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Community Manager</t>
+          <t>Plan de Internacionalización de Empresas (16) Manuales emprenemjunts para emprendedores y pymes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CEEI Elche</t>
+          <t>CEEI Valencia</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fichas</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>txt</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.048768</v>
+        <v>0.050268</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Fichas/Community Manager.pdf</t>
+          <t>data/raw/ceei_valencia/txt/330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes.txt</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>doc_0110</t>
+          <t>doc_0312</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes</t>
+          <t>Claves para Elaborar un Plan de Igualdad Manual de Gestión Empresarial elaborado por Sandra Merchán</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Ficha_HTML</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4156,11 +4156,11 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>0.045985</v>
+        <v>0.049948</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/330_plan_de_internacionalización_de_empresas_16_manuales_emprenemjunts_para_emprendedores_y_pymes.txt</t>
+          <t>data/raw/ceei_valencia/txt/18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán.txt</t>
         </is>
       </c>
     </row>
@@ -4180,35 +4180,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>doc_0052</t>
+          <t>doc_0050</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán</t>
+          <t>Community Manager</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CEEI Valencia</t>
+          <t>CEEI Elche</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fichas_HTML</t>
+          <t>Fichas</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>txt</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>0.045263</v>
+        <v>0.04875</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>data/raw/ceei_valencia/txt/18340_claves_para_elaborar_un_plan_de_igualdad_manual_de_gestión_empresarial_elaborado_por_sandra_merchán.txt</t>
+          <t>data/raw/ceei_elche/pdf/Fichas/Community Manager.pdf</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>doc_0323</t>
+          <t>doc_0190</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -4252,11 +4252,11 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.045255</v>
+        <v>0.045249</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Informes_y_Publicaciones/Análisis para la definición de las competencias del perfil profesional de un Agente de Desarrollo Local_.pdf</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>doc_0299</t>
+          <t>doc_0166</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>documentos_ceei_elche_PDF/Infografias/Fases Ecosistema Emprendimiento de la Comunitat Valenciana.pdf</t>
+          <t>data/raw/ceei_elche/pdf/Infografias/Fases Ecosistema Emprendimiento de la Comunitat Valenciana.pdf</t>
         </is>
       </c>
     </row>
